--- a/ttl_long/AdHoc_Net_19.xlsx
+++ b/ttl_long/AdHoc_Net_19.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C36"/>
+  <dimension ref="A1:C35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -443,12 +443,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>58</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>86</t>
         </is>
       </c>
     </row>
@@ -460,12 +460,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>277</t>
+          <t>234</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>37</t>
         </is>
       </c>
     </row>
@@ -477,12 +477,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>345</t>
+          <t>349</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
     </row>
@@ -494,12 +494,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
           <t>91</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>149</t>
         </is>
       </c>
     </row>
@@ -511,12 +511,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>276</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>212</t>
+          <t>133</t>
         </is>
       </c>
     </row>
@@ -528,12 +528,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>310</t>
+          <t>391</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>94</t>
+          <t>117</t>
         </is>
       </c>
     </row>
@@ -545,12 +545,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>103</t>
+          <t>19</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>278</t>
+          <t>349</t>
         </is>
       </c>
     </row>
@@ -562,12 +562,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>204</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>327</t>
+          <t>329</t>
         </is>
       </c>
     </row>
@@ -579,12 +579,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>365</t>
+          <t>282</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>256</t>
+          <t>288</t>
         </is>
       </c>
     </row>
@@ -596,12 +596,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>109</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>508</t>
+          <t>485</t>
         </is>
       </c>
     </row>
@@ -613,12 +613,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>97</t>
+          <t>83</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>337</t>
+          <t>550</t>
         </is>
       </c>
     </row>
@@ -630,12 +630,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>354</t>
+          <t>310</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>475</t>
+          <t>463</t>
         </is>
       </c>
     </row>
@@ -647,12 +647,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>23</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>639</t>
+          <t>603</t>
         </is>
       </c>
     </row>
@@ -664,12 +664,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>70</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>517</t>
+          <t>693</t>
         </is>
       </c>
     </row>
@@ -681,12 +681,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>311</t>
+          <t>279</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>563</t>
+          <t>612</t>
         </is>
       </c>
     </row>
@@ -698,12 +698,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>115</t>
+          <t>98</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>784</t>
+          <t>734</t>
         </is>
       </c>
     </row>
@@ -715,12 +715,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>234</t>
+          <t>150</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>768</t>
+          <t>654</t>
         </is>
       </c>
     </row>
@@ -732,12 +732,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>370</t>
+          <t>292</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>741</t>
+          <t>727</t>
         </is>
       </c>
     </row>
@@ -749,12 +749,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>109</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>804</t>
+          <t>899</t>
         </is>
       </c>
     </row>
@@ -766,12 +766,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>174</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>837</t>
+          <t>848</t>
         </is>
       </c>
     </row>
@@ -783,12 +783,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>302</t>
+          <t>372</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>907</t>
+          <t>870</t>
         </is>
       </c>
     </row>
@@ -800,12 +800,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>44</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>925</t>
+          <t>1026</t>
         </is>
       </c>
     </row>
@@ -817,12 +817,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>262</t>
+          <t>99</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>973</t>
+          <t>970</t>
         </is>
       </c>
     </row>
@@ -834,12 +834,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>324</t>
+          <t>321</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>1061</t>
+          <t>1019</t>
         </is>
       </c>
     </row>
@@ -851,12 +851,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>89</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>1162</t>
+          <t>1305</t>
         </is>
       </c>
     </row>
@@ -868,12 +868,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>229</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>1208</t>
+          <t>1125</t>
         </is>
       </c>
     </row>
@@ -885,12 +885,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>285</t>
+          <t>326</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>1120</t>
+          <t>1229</t>
         </is>
       </c>
     </row>
@@ -902,12 +902,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>66</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>1219</t>
+          <t>1339</t>
         </is>
       </c>
     </row>
@@ -919,12 +919,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>272</t>
+          <t>50</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>1219</t>
+          <t>1379</t>
         </is>
       </c>
     </row>
@@ -936,12 +936,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>299</t>
+          <t>298</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>1272</t>
+          <t>1319</t>
         </is>
       </c>
     </row>
@@ -953,12 +953,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>78</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>1523</t>
+          <t>1557</t>
         </is>
       </c>
     </row>
@@ -970,12 +970,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>178</t>
+          <t>77</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>1397</t>
+          <t>1561</t>
         </is>
       </c>
     </row>
@@ -987,12 +987,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>303</t>
+          <t>455</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>1440</t>
+          <t>96</t>
         </is>
       </c>
     </row>
@@ -1004,29 +1004,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>88</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>1547</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>496</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>42</t>
+          <t>1560</t>
         </is>
       </c>
     </row>
@@ -1041,7 +1024,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D89"/>
+  <dimension ref="A1:D88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1140,7 +1123,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1162,7 +1145,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1184,7 +1167,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>32</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1206,7 +1189,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1250,7 +1233,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>32</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1267,12 +1250,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1289,12 +1272,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1311,12 +1294,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1333,12 +1316,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>32</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1355,12 +1338,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
           <t>4</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>3</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1377,12 +1360,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>32</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1399,12 +1382,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1421,12 +1404,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1443,12 +1426,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>9</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1487,12 +1470,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>11</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1509,12 +1492,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1531,12 +1514,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1553,12 +1536,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1575,12 +1558,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>11</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1597,12 +1580,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1619,12 +1602,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>16</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1646,7 +1629,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>13</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1685,12 +1668,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>11</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1712,7 +1695,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>15</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1734,7 +1717,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1756,7 +1739,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>14</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1773,12 +1756,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>15</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1822,7 +1805,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>13</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1839,12 +1822,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>15</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1866,7 +1849,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>17</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1883,12 +1866,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1910,7 +1893,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>17</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1927,12 +1910,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
           <t>15</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>18</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1949,12 +1932,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>13</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1976,7 +1959,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>16</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1998,7 +1981,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>19</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -2015,12 +1998,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>18</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -2059,12 +2042,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>14</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -2081,12 +2064,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -2103,12 +2086,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>11</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -2125,7 +2108,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2147,12 +2130,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>17</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>16</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -2169,12 +2152,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>17</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>20</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -2191,12 +2174,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>23</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -2213,12 +2196,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>22</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -2235,12 +2218,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>19</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -2257,12 +2240,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>22</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -2279,12 +2262,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>16</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -2301,12 +2284,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>23</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -2323,7 +2306,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2345,12 +2328,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>23</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -2367,12 +2350,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>21</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>18</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -2389,12 +2372,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>21</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>19</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -2411,12 +2394,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>21</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>22</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -2433,12 +2416,12 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>21</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>25</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -2455,12 +2438,12 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
           <t>23</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>29</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -2477,12 +2460,12 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>22</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>15</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -2499,7 +2482,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>23</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2543,12 +2526,12 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
           <t>25</t>
-        </is>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>31</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -2565,12 +2548,12 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>24</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>26</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -2587,7 +2570,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>24</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -2609,12 +2592,12 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
           <t>26</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>27</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -2631,12 +2614,12 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>25</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>29</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -2653,12 +2636,12 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>26</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>23</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -2675,12 +2658,12 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>26</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>29</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -2702,7 +2685,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>33</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -2724,7 +2707,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>28</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -2741,12 +2724,12 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>27</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>29</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -2768,7 +2751,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>33</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -2790,7 +2773,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>31</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -2812,7 +2795,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>24</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -2829,12 +2812,12 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>30</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>31</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -2851,12 +2834,12 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>30</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>24</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -2878,7 +2861,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>28</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -2900,7 +2883,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>27</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -2917,12 +2900,12 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>31</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>27</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -2961,12 +2944,12 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>33</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>30</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -2975,28 +2958,6 @@
         </is>
       </c>
       <c r="D88" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D89" t="inlineStr">
         <is>
           <t>3000</t>
         </is>
@@ -3035,7 +2996,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5</v>
+        <v>32</v>
       </c>
     </row>
     <row r="3">
@@ -3045,7 +3006,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
     </row>
     <row r="4">
@@ -3071,7 +3032,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>jamm_powe</t>
+          <t>jamm_power</t>
         </is>
       </c>
       <c r="B6" t="n">

--- a/ttl_long/AdHoc_Net_19.xlsx
+++ b/ttl_long/AdHoc_Net_19.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C35"/>
+  <dimension ref="A1:C42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -443,12 +443,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>112</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>86</t>
+          <t>18</t>
         </is>
       </c>
     </row>
@@ -460,12 +460,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>234</t>
+          <t>218</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>51</t>
         </is>
       </c>
     </row>
@@ -477,12 +477,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>349</t>
+          <t>374</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>14</t>
         </is>
       </c>
     </row>
@@ -494,12 +494,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>67</t>
         </is>
       </c>
     </row>
@@ -511,12 +511,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>276</t>
+          <t>171</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>133</t>
+          <t>107</t>
         </is>
       </c>
     </row>
@@ -528,12 +528,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>391</t>
+          <t>327</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>117</t>
+          <t>157</t>
         </is>
       </c>
     </row>
@@ -545,12 +545,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>53</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>349</t>
+          <t>189</t>
         </is>
       </c>
     </row>
@@ -562,12 +562,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>204</t>
+          <t>121</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>329</t>
+          <t>326</t>
         </is>
       </c>
     </row>
@@ -579,12 +579,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>282</t>
+          <t>303</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>288</t>
+          <t>205</t>
         </is>
       </c>
     </row>
@@ -596,12 +596,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>109</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>485</t>
+          <t>422</t>
         </is>
       </c>
     </row>
@@ -613,12 +613,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>192</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>550</t>
+          <t>307</t>
         </is>
       </c>
     </row>
@@ -630,12 +630,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>310</t>
+          <t>321</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>463</t>
+          <t>338</t>
         </is>
       </c>
     </row>
@@ -647,12 +647,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>41</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>603</t>
+          <t>532</t>
         </is>
       </c>
     </row>
@@ -664,12 +664,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>57</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>693</t>
+          <t>471</t>
         </is>
       </c>
     </row>
@@ -681,12 +681,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>279</t>
+          <t>315</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>612</t>
+          <t>525</t>
         </is>
       </c>
     </row>
@@ -698,12 +698,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>98</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>734</t>
+          <t>660</t>
         </is>
       </c>
     </row>
@@ -715,12 +715,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>179</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>654</t>
+          <t>706</t>
         </is>
       </c>
     </row>
@@ -732,12 +732,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>292</t>
+          <t>335</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>727</t>
+          <t>660</t>
         </is>
       </c>
     </row>
@@ -749,12 +749,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>109</t>
+          <t>81</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>726</t>
         </is>
       </c>
     </row>
@@ -766,12 +766,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>174</t>
+          <t>143</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>848</t>
+          <t>715</t>
         </is>
       </c>
     </row>
@@ -783,12 +783,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>372</t>
+          <t>311</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>870</t>
+          <t>774</t>
         </is>
       </c>
     </row>
@@ -800,12 +800,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>48</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>1026</t>
+          <t>920</t>
         </is>
       </c>
     </row>
@@ -817,12 +817,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>154</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>970</t>
+          <t>853</t>
         </is>
       </c>
     </row>
@@ -834,12 +834,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>321</t>
+          <t>364</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>1019</t>
+          <t>862</t>
         </is>
       </c>
     </row>
@@ -851,12 +851,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>12</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>1305</t>
+          <t>1004</t>
         </is>
       </c>
     </row>
@@ -868,12 +868,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>229</t>
+          <t>218</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>1125</t>
+          <t>989</t>
         </is>
       </c>
     </row>
@@ -885,12 +885,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>326</t>
+          <t>345</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>1229</t>
+          <t>1005</t>
         </is>
       </c>
     </row>
@@ -902,12 +902,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>88</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>1339</t>
+          <t>1164</t>
         </is>
       </c>
     </row>
@@ -919,12 +919,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>121</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>1379</t>
+          <t>1040</t>
         </is>
       </c>
     </row>
@@ -936,12 +936,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>298</t>
+          <t>287</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>1319</t>
+          <t>1114</t>
         </is>
       </c>
     </row>
@@ -953,12 +953,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>77</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>1557</t>
+          <t>1277</t>
         </is>
       </c>
     </row>
@@ -970,12 +970,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>186</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>1561</t>
+          <t>1242</t>
         </is>
       </c>
     </row>
@@ -987,12 +987,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>455</t>
+          <t>385</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>96</t>
+          <t>1277</t>
         </is>
       </c>
     </row>
@@ -1004,12 +1004,131 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>109</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>1560</t>
+          <t>1426</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>206</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>1328</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>372</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>1399</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>1443</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>105</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>1466</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>280</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>1503</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>1585</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>168</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>1651</t>
         </is>
       </c>
     </row>
@@ -1024,7 +1143,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D88"/>
+  <dimension ref="A1:D118"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1118,12 +1237,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1145,7 +1264,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1167,7 +1286,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1184,12 +1303,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
           <t>2</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>4</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1211,7 +1330,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1233,7 +1352,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1250,12 +1369,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1272,12 +1391,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1294,12 +1413,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
           <t>4</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>1</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1316,12 +1435,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1338,12 +1457,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1360,12 +1479,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1382,12 +1501,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1404,12 +1523,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>11</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1426,12 +1545,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1448,7 +1567,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1470,12 +1589,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>9</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1497,7 +1616,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>13</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1519,7 +1638,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1536,7 +1655,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1558,12 +1677,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
           <t>8</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>11</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1580,12 +1699,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1602,12 +1721,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1624,12 +1743,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>11</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1646,12 +1765,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1668,12 +1787,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>13</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1690,12 +1809,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
           <t>10</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>15</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1712,12 +1831,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1734,7 +1853,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1756,12 +1875,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>11</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1778,12 +1897,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>14</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1800,7 +1919,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1822,12 +1941,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1844,12 +1963,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
           <t>13</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>17</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1866,12 +1985,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1888,12 +2007,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1910,12 +2029,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>19</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1932,12 +2051,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>15</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1954,7 +2073,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1976,12 +2095,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>20</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -2003,7 +2122,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>16</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -2020,12 +2139,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>12</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -2042,12 +2161,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>22</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -2064,12 +2183,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>19</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -2091,7 +2210,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>19</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -2108,12 +2227,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>21</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -2130,12 +2249,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
           <t>17</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>16</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -2157,7 +2276,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>14</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -2174,7 +2293,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2196,12 +2315,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>19</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -2223,7 +2342,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>22</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -2240,12 +2359,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>21</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -2262,7 +2381,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2284,12 +2403,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>12</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -2306,12 +2425,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>22</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -2333,7 +2452,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>26</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -2350,7 +2469,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2372,7 +2491,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2394,7 +2513,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2421,7 +2540,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>24</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -2438,12 +2557,12 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>21</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>25</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -2465,7 +2584,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>16</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -2482,7 +2601,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>22</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2504,12 +2623,12 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
           <t>24</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>27</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -2526,7 +2645,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>23</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2548,12 +2667,12 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>23</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>20</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -2570,12 +2689,12 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>23</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>26</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -2592,12 +2711,12 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
           <t>25</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>26</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -2614,12 +2733,12 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>24</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>28</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -2636,12 +2755,12 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>24</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>27</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -2658,12 +2777,12 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>25</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>28</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -2680,12 +2799,12 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
           <t>27</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>33</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -2702,12 +2821,12 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>26</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>29</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -2724,12 +2843,12 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>26</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>28</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -2746,12 +2865,12 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>27</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>21</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -2768,12 +2887,12 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>27</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>30</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -2790,12 +2909,12 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>27</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>34</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -2812,12 +2931,12 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>28</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>29</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -2834,12 +2953,12 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>28</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>27</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -2856,12 +2975,12 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
           <t>30</t>
-        </is>
-      </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>28</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -2878,12 +2997,12 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>29</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>32</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -2900,12 +3019,12 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>29</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>34</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -2922,12 +3041,12 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>29</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>25</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -2944,20 +3063,680 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
           <t>33</t>
         </is>
       </c>
-      <c r="B88" t="inlineStr">
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D88" t="inlineStr">
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
         <is>
           <t>3000</t>
         </is>
@@ -2996,7 +3775,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>32</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3">
@@ -3006,7 +3785,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>29</v>
+        <v>38</v>
       </c>
     </row>
     <row r="4">
@@ -3026,7 +3805,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>800</v>
+        <v>250</v>
       </c>
     </row>
     <row r="6">

--- a/ttl_long/AdHoc_Net_19.xlsx
+++ b/ttl_long/AdHoc_Net_19.xlsx
@@ -443,12 +443,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>112</t>
+          <t>62</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>53</t>
         </is>
       </c>
     </row>
@@ -460,12 +460,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>218</t>
+          <t>144</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>73</t>
         </is>
       </c>
     </row>
@@ -477,12 +477,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>374</t>
+          <t>376</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>32</t>
         </is>
       </c>
     </row>
@@ -494,12 +494,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>98</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>76</t>
         </is>
       </c>
     </row>
@@ -511,12 +511,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>171</t>
+          <t>261</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>107</t>
+          <t>128</t>
         </is>
       </c>
     </row>
@@ -528,12 +528,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>327</t>
+          <t>372</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>157</t>
+          <t>136</t>
         </is>
       </c>
     </row>
@@ -545,12 +545,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>38</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>189</t>
+          <t>295</t>
         </is>
       </c>
     </row>
@@ -562,12 +562,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>121</t>
+          <t>253</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>326</t>
+          <t>273</t>
         </is>
       </c>
     </row>
@@ -579,12 +579,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>303</t>
+          <t>276</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>205</t>
+          <t>230</t>
         </is>
       </c>
     </row>
@@ -596,12 +596,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>109</t>
+          <t>22</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>422</t>
+          <t>316</t>
         </is>
       </c>
     </row>
@@ -613,12 +613,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>192</t>
+          <t>157</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>307</t>
+          <t>291</t>
         </is>
       </c>
     </row>
@@ -630,12 +630,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>321</t>
+          <t>345</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>338</t>
+          <t>358</t>
         </is>
       </c>
     </row>
@@ -647,12 +647,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>532</t>
+          <t>498</t>
         </is>
       </c>
     </row>
@@ -664,12 +664,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>66</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>471</t>
+          <t>551</t>
         </is>
       </c>
     </row>
@@ -681,12 +681,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>315</t>
+          <t>284</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>525</t>
+          <t>535</t>
         </is>
       </c>
     </row>
@@ -698,12 +698,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>12</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>660</t>
+          <t>542</t>
         </is>
       </c>
     </row>
@@ -715,12 +715,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>179</t>
+          <t>123</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>706</t>
+          <t>575</t>
         </is>
       </c>
     </row>
@@ -732,12 +732,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>335</t>
+          <t>369</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>660</t>
+          <t>637</t>
         </is>
       </c>
     </row>
@@ -749,12 +749,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>110</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>726</t>
+          <t>811</t>
         </is>
       </c>
     </row>
@@ -766,12 +766,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>143</t>
+          <t>239</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>715</t>
+          <t>814</t>
         </is>
       </c>
     </row>
@@ -783,12 +783,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>311</t>
+          <t>368</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>774</t>
+          <t>761</t>
         </is>
       </c>
     </row>
@@ -800,12 +800,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>45</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>920</t>
+          <t>842</t>
         </is>
       </c>
     </row>
@@ -817,12 +817,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>154</t>
+          <t>224</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>853</t>
+          <t>899</t>
         </is>
       </c>
     </row>
@@ -834,12 +834,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>364</t>
+          <t>380</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>862</t>
+          <t>847</t>
         </is>
       </c>
     </row>
@@ -851,12 +851,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>33</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>1004</t>
+          <t>1054</t>
         </is>
       </c>
     </row>
@@ -868,12 +868,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>218</t>
+          <t>98</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>989</t>
+          <t>962</t>
         </is>
       </c>
     </row>
@@ -885,12 +885,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>345</t>
+          <t>373</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>1005</t>
+          <t>954</t>
         </is>
       </c>
     </row>
@@ -902,12 +902,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>39</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>1164</t>
+          <t>1032</t>
         </is>
       </c>
     </row>
@@ -919,12 +919,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>121</t>
+          <t>131</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>1040</t>
+          <t>1043</t>
         </is>
       </c>
     </row>
@@ -936,12 +936,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>287</t>
+          <t>322</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>1114</t>
+          <t>1147</t>
         </is>
       </c>
     </row>
@@ -953,12 +953,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>58</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>1277</t>
+          <t>1267</t>
         </is>
       </c>
     </row>
@@ -970,12 +970,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>186</t>
+          <t>76</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>1242</t>
+          <t>1263</t>
         </is>
       </c>
     </row>
@@ -987,12 +987,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>385</t>
+          <t>428</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>1277</t>
+          <t>1001</t>
         </is>
       </c>
     </row>
@@ -1004,12 +1004,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>109</t>
+          <t>72</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>1426</t>
+          <t>1333</t>
         </is>
       </c>
     </row>
@@ -1021,12 +1021,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>206</t>
+          <t>138</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>1328</t>
+          <t>1395</t>
         </is>
       </c>
     </row>
@@ -1038,12 +1038,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>372</t>
+          <t>277</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>1399</t>
+          <t>1405</t>
         </is>
       </c>
     </row>
@@ -1055,12 +1055,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>115</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>1443</t>
+          <t>1474</t>
         </is>
       </c>
     </row>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>105</t>
+          <t>227</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>1466</t>
+          <t>1496</t>
         </is>
       </c>
     </row>
@@ -1089,12 +1089,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>280</t>
+          <t>366</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>1503</t>
+          <t>1488</t>
         </is>
       </c>
     </row>
@@ -1106,12 +1106,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>37</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>1585</t>
+          <t>1633</t>
         </is>
       </c>
     </row>
@@ -1123,12 +1123,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>168</t>
+          <t>72</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>1651</t>
+          <t>1678</t>
         </is>
       </c>
     </row>
@@ -1143,7 +1143,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D118"/>
+  <dimension ref="A1:D112"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1286,7 +1286,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1330,7 +1330,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1352,7 +1352,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1374,7 +1374,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1391,12 +1391,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1440,7 +1440,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1457,12 +1457,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1479,7 +1479,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1506,7 +1506,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1523,12 +1523,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
           <t>5</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>11</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1550,7 +1550,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1572,7 +1572,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1594,7 +1594,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>15</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1611,12 +1611,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1633,12 +1633,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1655,12 +1655,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
           <t>7</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>4</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1682,7 +1682,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1699,12 +1699,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1721,12 +1721,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1748,7 +1748,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1770,7 +1770,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1787,12 +1787,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>11</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1836,7 +1836,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>12</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1858,7 +1858,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>13</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1875,12 +1875,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1897,12 +1897,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1919,12 +1919,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
           <t>10</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>13</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1946,7 +1946,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1963,12 +1963,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1990,7 +1990,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>13</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2012,7 +2012,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2034,7 +2034,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>16</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2051,7 +2051,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2073,12 +2073,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -2095,12 +2095,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>16</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -2117,12 +2117,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>14</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -2139,12 +2139,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>20</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -2161,12 +2161,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>11</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -2183,12 +2183,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>17</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -2205,12 +2205,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
           <t>16</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>19</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -2227,12 +2227,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
           <t>16</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>21</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -2249,12 +2249,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>9</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -2271,12 +2271,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>18</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -2298,7 +2298,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>19</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -2320,7 +2320,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>20</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -2337,12 +2337,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>23</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -2364,7 +2364,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>25</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>21</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -2408,7 +2408,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>28</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -2430,7 +2430,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>23</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -2447,12 +2447,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>18</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -2469,12 +2469,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>21</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -2491,12 +2491,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>26</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -2518,7 +2518,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>19</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -2535,12 +2535,12 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>26</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -2557,12 +2557,12 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>32</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -2579,12 +2579,12 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>21</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>25</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -2601,12 +2601,12 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>21</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>27</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -2628,7 +2628,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>32</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -2645,12 +2645,12 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>22</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>28</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -2667,12 +2667,12 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>22</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>26</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -2689,12 +2689,12 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>22</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>18</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -2711,12 +2711,12 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>23</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>22</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -2733,12 +2733,12 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>23</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>26</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -2755,12 +2755,12 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>23</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>20</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -2777,12 +2777,12 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>24</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>30</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -2799,12 +2799,12 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>24</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>28</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -2821,12 +2821,12 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>24</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>22</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -2843,12 +2843,12 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>24</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>31</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -2865,12 +2865,12 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>25</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>24</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -2887,12 +2887,12 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>25</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>22</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -2909,12 +2909,12 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
           <t>27</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>34</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -2931,7 +2931,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>26</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -2953,12 +2953,12 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>26</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>32</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -2975,7 +2975,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>27</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -2997,12 +2997,12 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>27</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>31</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -3019,12 +3019,12 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>27</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>28</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -3041,12 +3041,12 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>28</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>30</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -3063,12 +3063,12 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>28</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>31</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -3085,12 +3085,12 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>29</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>28</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -3107,12 +3107,12 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>29</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>32</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -3129,12 +3129,12 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
           <t>31</t>
-        </is>
-      </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>35</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -3151,12 +3151,12 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>30</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>36</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -3178,7 +3178,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>34</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -3222,7 +3222,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>23</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -3239,12 +3239,12 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>33</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>31</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -3261,12 +3261,12 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>33</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>30</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -3288,7 +3288,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>37</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -3310,7 +3310,7 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>35</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -3327,12 +3327,12 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>37</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -3349,7 +3349,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -3376,7 +3376,7 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>38</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -3420,7 +3420,7 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>37</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -3464,7 +3464,7 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>39</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -3481,12 +3481,12 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>37</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>40</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -3508,7 +3508,7 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>39</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -3530,7 +3530,7 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>38</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -3547,12 +3547,12 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>38</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>36</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -3569,12 +3569,12 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>39</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>40</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -3591,12 +3591,12 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>40</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>36</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -3605,138 +3605,6 @@
         </is>
       </c>
       <c r="D112" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="B113" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="C113" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D113" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="B114" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="C114" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D114" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="B115" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="C115" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D115" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="B116" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="C116" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D116" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="B117" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="C117" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D117" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="B118" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="C118" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D118" t="inlineStr">
         <is>
           <t>3000</t>
         </is>
@@ -3775,7 +3643,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3">
